--- a/Scripts/Ammonia breakdown.xlsx
+++ b/Scripts/Ammonia breakdown.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20395"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20399"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Natural gas vs. green chemicals\Scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Fossil vs. green chemicals\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5E416F-A8EE-4B88-A570-314412913A5A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFA7C4A-45D9-4583-BDD0-9553E0ECCEDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAU breakdown" sheetId="2" r:id="rId1"/>
@@ -326,7 +326,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2931,7 +2931,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="612513504"/>
@@ -2990,7 +2990,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="612510592"/>
@@ -3032,7 +3032,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3069,7 +3069,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3120,7 +3120,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5725,7 +5725,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1368817216"/>
@@ -5784,7 +5784,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1368803904"/>
@@ -5826,7 +5826,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5863,7 +5863,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5914,7 +5914,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7679,7 +7679,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1524527328"/>
@@ -7738,7 +7738,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1524533568"/>
@@ -7780,7 +7780,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -7817,7 +7817,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -7868,7 +7868,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -10665,7 +10665,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1130028784"/>
@@ -10724,7 +10724,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1130030032"/>
@@ -10766,7 +10766,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -10803,7 +10803,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -12998,13 +12998,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
@@ -13456,22 +13456,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75A59A6-D3AD-48FF-B7C0-E675D467F6FD}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:X48"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
@@ -13506,7 +13509,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
@@ -13543,20 +13546,12 @@
       <c r="L2" s="2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <f>B2/J2*100</f>
-        <v>36.549178500985327</v>
-      </c>
-      <c r="N2">
-        <f>F2/J2*100</f>
-        <v>9.8321884858812858</v>
-      </c>
-      <c r="O2">
-        <f>H2/J2*100</f>
-        <v>28.305542587037635</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M2" s="2">
+        <f>(H2+I2)/J2*100</f>
+        <v>42.81414442870696</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
@@ -13593,20 +13588,12 @@
       <c r="L3" s="2">
         <v>0</v>
       </c>
-      <c r="M3">
-        <f t="shared" ref="M3:M48" si="0">B3/J3*100</f>
-        <v>32.626209030655964</v>
-      </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N48" si="1">F3/J3*100</f>
-        <v>9.2367236837876803</v>
-      </c>
-      <c r="O3">
-        <f t="shared" ref="O3:O48" si="2">H3/J3*100</f>
-        <v>30.690846473719564</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M3" s="2">
+        <f t="shared" ref="M3:M48" si="0">(H3+I3)/J3*100</f>
+        <v>46.422086046385871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
@@ -13643,20 +13630,12 @@
       <c r="L4" s="2">
         <v>0</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <f t="shared" si="0"/>
-        <v>30.281973512413728</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="1"/>
-        <v>7.1121077368383077</v>
-      </c>
-      <c r="O4">
-        <f t="shared" si="2"/>
-        <v>33.049975350282736</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+        <v>49.990436101380517</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -13693,20 +13672,12 @@
       <c r="L5" s="2">
         <v>0</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <f t="shared" si="0"/>
-        <v>28.774178720104533</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="1"/>
-        <v>8.5934561714880271</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="2"/>
-        <v>33.063936513798765</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+        <v>50.01155335321662</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -13743,20 +13714,12 @@
       <c r="L6" s="2">
         <v>0</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <f t="shared" si="0"/>
-        <v>26.219059286267214</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="1"/>
-        <v>9.0833134062342094</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="2"/>
-        <v>34.154198682837169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+        <v>51.660652353062034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -13793,20 +13756,12 @@
       <c r="L7" s="2">
         <v>0</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <f t="shared" si="0"/>
-        <v>23.026098667212771</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="1"/>
-        <v>8.284949307189299</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="2"/>
-        <v>36.261238818664296</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+        <v>54.847700275390032</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -13843,20 +13798,12 @@
       <c r="L8" s="2">
         <v>0</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <f t="shared" si="0"/>
-        <v>22.756469330734376</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="1"/>
-        <v>9.9214872909915997</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="2"/>
-        <v>35.539640956966849</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+        <v>53.756232236041846</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
@@ -13893,20 +13840,12 @@
       <c r="L9" s="2">
         <v>0</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <f t="shared" si="0"/>
-        <v>23.213708598508166</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="1"/>
-        <v>9.2312619681560619</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="2"/>
-        <v>35.662635452222275</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+        <v>53.942270149556812</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -13943,20 +13882,12 @@
       <c r="L10" s="2">
         <v>0</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <f t="shared" si="0"/>
-        <v>25.763464894367605</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="1"/>
-        <v>8.7000489550185236</v>
-      </c>
-      <c r="O10">
-        <f t="shared" si="2"/>
-        <v>34.597036431097131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+        <v>52.33047591338368</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -13993,20 +13924,12 @@
       <c r="L11" s="2">
         <v>0</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="2">
         <f t="shared" si="0"/>
-        <v>29.353977051965014</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="1"/>
-        <v>8.519448030898694</v>
-      </c>
-      <c r="O11">
-        <f t="shared" si="2"/>
-        <v>32.796927360551152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>49.607683036448158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -14043,20 +13966,12 @@
       <c r="L12" s="2">
         <v>0</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="2">
         <f t="shared" si="0"/>
-        <v>29.447358570618469</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="1"/>
-        <v>9.3175890930087704</v>
-      </c>
-      <c r="O12">
-        <f t="shared" si="2"/>
-        <v>32.326288163708384</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+        <v>48.895807809697885</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -14093,20 +14008,12 @@
       <c r="L13" s="2">
         <v>0</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <f t="shared" si="0"/>
-        <v>27.831426905416269</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="1"/>
-        <v>7.6544980277158254</v>
-      </c>
-      <c r="O13">
-        <f t="shared" si="2"/>
-        <v>34.057300543661469</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+        <v>51.514087032408497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -14143,20 +14050,12 @@
       <c r="L14" s="2">
         <v>0</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="2">
         <f t="shared" si="0"/>
-        <v>23.373558385802419</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="1"/>
-        <v>8.9519695486074422</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="2"/>
-        <v>35.72568981082847</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>54.037644347310632</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -14193,20 +14092,12 @@
       <c r="L15" s="2">
         <v>0</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <f t="shared" si="0"/>
-        <v>20.362601647250099</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>6.0934497718807084</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="2"/>
-        <v>38.824215605511718</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>58.724384779214375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -14243,20 +14134,12 @@
       <c r="L16" s="2">
         <v>0</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <f t="shared" si="0"/>
-        <v>19.256433952129289</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="1"/>
-        <v>6.3365946788897727</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="2"/>
-        <v>39.279809620310587</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>59.413503099079612</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -14293,20 +14176,12 @@
       <c r="L17" s="2">
         <v>0</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="2">
         <f t="shared" si="0"/>
-        <v>15.930572911117219</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="1"/>
-        <v>5.0921419162015562</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="2"/>
-        <v>41.692500969138479</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>63.062870199285406</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
@@ -14343,20 +14218,12 @@
       <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="2">
         <f t="shared" si="0"/>
-        <v>12.353783079064504</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="1"/>
-        <v>5.4693552620319954</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="2"/>
-        <v>43.381573282285032</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>65.617712090876751</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -14393,20 +14260,12 @@
       <c r="L19" s="2">
         <v>0</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="2">
         <f t="shared" si="0"/>
-        <v>13.155320684212271</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="1"/>
-        <v>7.8368631479958211</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="2"/>
-        <v>41.708618433045451</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>63.087249008679912</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -14443,20 +14302,12 @@
       <c r="L20" s="2">
         <v>0</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="2">
         <f t="shared" si="0"/>
-        <v>13.328177316167711</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="1"/>
-        <v>8.8493682261001645</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="2"/>
-        <v>41.082860100920072</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>62.14074506773968</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -14493,20 +14344,12 @@
       <c r="L21" s="2">
         <v>0</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="2">
         <f t="shared" si="0"/>
-        <v>19.380905384483853</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="1"/>
-        <v>9.3970076296609175</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="2"/>
-        <v>37.598493341335818</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>56.870392760282328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -14543,20 +14386,12 @@
       <c r="L22" s="2">
         <v>0</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="2">
         <f t="shared" si="0"/>
-        <v>24.388512768211147</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="1"/>
-        <v>10.718929964336645</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="2"/>
-        <v>34.257103176534457</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>51.816302711714272</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -14593,20 +14428,12 @@
       <c r="L23" s="2">
         <v>0</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="2">
         <f t="shared" si="0"/>
-        <v>29.194326406594108</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="1"/>
-        <v>8.0581966865795671</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="2"/>
-        <v>33.124704603720382</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>50.103469407132941</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -14643,20 +14470,12 @@
       <c r="L24" s="2">
         <v>0</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="2">
         <f t="shared" si="0"/>
-        <v>28.652286196972927</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="1"/>
-        <v>9.1290634638212236</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="2"/>
-        <v>32.845534433021108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>49.681204687361088</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -14693,20 +14512,12 @@
       <c r="L25" s="2">
         <v>0</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="2">
         <f t="shared" si="0"/>
-        <v>32.373932901894413</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="1"/>
-        <v>9.562392973235859</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="2"/>
-        <v>30.65210185979209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>46.363482064800834</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>20</v>
       </c>
@@ -14743,20 +14554,12 @@
       <c r="L26" s="2">
         <v>0</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="2">
         <f t="shared" si="0"/>
-        <v>33.273699753625621</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="1"/>
-        <v>9.6028230519503808</v>
-      </c>
-      <c r="O26">
-        <f t="shared" si="2"/>
-        <v>30.155767232081317</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>45.612740673059811</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -14793,20 +14596,12 @@
       <c r="L27" s="2">
         <v>0</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="2">
         <f t="shared" si="0"/>
-        <v>29.936439548854</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="1"/>
-        <v>9.4084514030433866</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="2"/>
-        <v>32.020133222380878</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>48.432726706933202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>18</v>
       </c>
@@ -14843,20 +14638,12 @@
       <c r="L28" s="2">
         <v>0</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="2">
         <f t="shared" si="0"/>
-        <v>29.922699296181403</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="1"/>
-        <v>9.1533235084878992</v>
-      </c>
-      <c r="O28">
-        <f t="shared" si="2"/>
-        <v>32.162070052247429</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>48.647416247505454</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>
@@ -14893,20 +14680,12 @@
       <c r="L29" s="2">
         <v>0</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="2">
         <f t="shared" si="0"/>
-        <v>32.852920742830719</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="1"/>
-        <v>9.7993934302971315</v>
-      </c>
-      <c r="O29">
-        <f t="shared" si="2"/>
-        <v>30.274128082358654</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>45.791769869299245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
@@ -14943,20 +14722,12 @@
       <c r="L30" s="2">
         <v>0</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="2">
         <f t="shared" si="0"/>
-        <v>37.897879266743601</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="1"/>
-        <v>9.0154906916591067</v>
-      </c>
-      <c r="O30">
-        <f t="shared" si="2"/>
-        <v>28.024695576940289</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>42.389343370196791</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
@@ -14993,20 +14764,12 @@
       <c r="L31" s="2">
         <v>0</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="2">
         <f t="shared" si="0"/>
-        <v>40.035382366895512</v>
-      </c>
-      <c r="N31">
-        <f t="shared" si="1"/>
-        <v>11.451999961216869</v>
-      </c>
-      <c r="O31">
-        <f t="shared" si="2"/>
-        <v>25.61005173675246</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>38.73702298807374</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>14</v>
       </c>
@@ -15043,20 +14806,12 @@
       <c r="L32" s="2">
         <v>0</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="2">
         <f t="shared" si="0"/>
-        <v>44.327410201576406</v>
-      </c>
-      <c r="N32">
-        <f t="shared" si="1"/>
-        <v>11.448082601045511</v>
-      </c>
-      <c r="O32">
-        <f t="shared" si="2"/>
-        <v>23.346336926559122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+        <v>35.312993488162157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
@@ -15093,20 +14848,12 @@
       <c r="L33" s="2">
         <v>0</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="2">
         <f t="shared" si="0"/>
-        <v>49.45159716035004</v>
-      </c>
-      <c r="N33">
-        <f t="shared" si="1"/>
-        <v>10.54818560781537</v>
-      </c>
-      <c r="O33">
-        <f t="shared" si="2"/>
-        <v>21.116313279921222</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+        <v>31.939924267072232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>12</v>
       </c>
@@ -15143,20 +14890,12 @@
       <c r="L34" s="2">
         <v>0</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="2">
         <f t="shared" si="0"/>
-        <v>56.504150093734509</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="1"/>
-        <v>12.619055895062228</v>
-      </c>
-      <c r="O34">
-        <f t="shared" si="2"/>
-        <v>16.300012863461628</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+        <v>24.654927662316343</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>11</v>
       </c>
@@ -15193,20 +14932,12 @@
       <c r="L35" s="2">
         <v>0</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="2">
         <f t="shared" si="0"/>
-        <v>63.267988190350124</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="1"/>
-        <v>11.30060567335622</v>
-      </c>
-      <c r="O35">
-        <f t="shared" si="2"/>
-        <v>13.425365567652396</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+        <v>20.306819367768746</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>10</v>
       </c>
@@ -15243,20 +14974,12 @@
       <c r="L36" s="2">
         <v>0</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="2">
         <f t="shared" si="0"/>
-        <v>58.633739372394132</v>
-      </c>
-      <c r="N36">
-        <f t="shared" si="1"/>
-        <v>14.870775780217189</v>
-      </c>
-      <c r="O36">
-        <f t="shared" si="2"/>
-        <v>13.98709800244764</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+        <v>21.156479589601997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>9</v>
       </c>
@@ -15293,20 +15016,12 @@
       <c r="L37" s="2">
         <v>0</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="2">
         <f t="shared" si="0"/>
-        <v>64.139132528475784</v>
-      </c>
-      <c r="N37">
-        <f t="shared" si="1"/>
-        <v>14.811225683057962</v>
-      </c>
-      <c r="O37">
-        <f t="shared" si="2"/>
-        <v>11.112210412738003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+        <v>16.808007833455829</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>8</v>
       </c>
@@ -15343,20 +15058,12 @@
       <c r="L38" s="2">
         <v>0</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="2">
         <f t="shared" si="0"/>
-        <v>57.272282471463413</v>
-      </c>
-      <c r="N38">
-        <f t="shared" si="1"/>
-        <v>13.52153529358557</v>
-      </c>
-      <c r="O38">
-        <f t="shared" si="2"/>
-        <v>15.418088612100508</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+        <v>23.320954566522527</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
@@ -15393,20 +15100,12 @@
       <c r="L39" s="2">
         <v>0</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="2">
         <f t="shared" si="0"/>
-        <v>58.234012184487796</v>
-      </c>
-      <c r="N39">
-        <f t="shared" si="1"/>
-        <v>10.946066296411692</v>
-      </c>
-      <c r="O39">
-        <f t="shared" si="2"/>
-        <v>16.269989592505592</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+        <v>24.609515331675393</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -15443,20 +15142,12 @@
       <c r="L40" s="2">
         <v>0</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="2">
         <f t="shared" si="0"/>
-        <v>63.451022841152593</v>
-      </c>
-      <c r="N40">
-        <f t="shared" si="1"/>
-        <v>14.9776101598562</v>
-      </c>
-      <c r="O40">
-        <f t="shared" si="2"/>
-        <v>11.387631741767937</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+        <v>17.224602163826805</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
@@ -15493,20 +15184,12 @@
       <c r="L41" s="2">
         <v>0</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="2">
         <f t="shared" si="0"/>
-        <v>60.516171892102875</v>
-      </c>
-      <c r="N41">
-        <f t="shared" si="1"/>
-        <v>12.399502083485611</v>
-      </c>
-      <c r="O41">
-        <f t="shared" si="2"/>
-        <v>14.297950183426188</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+        <v>21.626665601103817</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
@@ -15543,20 +15226,12 @@
       <c r="L42" s="2">
         <v>0</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="2">
         <f t="shared" si="0"/>
-        <v>57.606803114256557</v>
-      </c>
-      <c r="N42">
-        <f t="shared" si="1"/>
-        <v>13.932875339462885</v>
-      </c>
-      <c r="O42">
-        <f t="shared" si="2"/>
-        <v>15.024345051312821</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+        <v>22.725389453167047</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>3</v>
       </c>
@@ -15593,26 +15268,18 @@
       <c r="L43" s="2">
         <v>0</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="2">
         <f t="shared" si="0"/>
-        <v>59.248480892312493</v>
-      </c>
-      <c r="N43">
-        <f t="shared" si="1"/>
-        <v>15.309139720993075</v>
-      </c>
-      <c r="O43">
-        <f t="shared" si="2"/>
-        <v>13.431158401021737</v>
-      </c>
-      <c r="W43" t="s">
+        <v>20.315581439852824</v>
+      </c>
+      <c r="T43" t="s">
         <v>61</v>
       </c>
-      <c r="X43">
+      <c r="U43">
         <v>3.9582000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>2</v>
       </c>
@@ -15649,26 +15316,18 @@
       <c r="L44" s="2">
         <v>0</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="2">
         <f t="shared" si="0"/>
-        <v>65.579651664632848</v>
-      </c>
-      <c r="N44">
-        <f t="shared" si="1"/>
-        <v>16.008376660813138</v>
-      </c>
-      <c r="O44">
-        <f t="shared" si="2"/>
-        <v>9.719771263429374</v>
-      </c>
-      <c r="W44" t="s">
+        <v>14.70184467960107</v>
+      </c>
+      <c r="T44" t="s">
         <v>62</v>
       </c>
-      <c r="X44">
+      <c r="U44">
         <v>1.0304</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>1</v>
       </c>
@@ -15705,20 +15364,12 @@
       <c r="L45" s="2">
         <v>0</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="2">
         <f t="shared" si="0"/>
-        <v>67.930414194173366</v>
-      </c>
-      <c r="N45">
-        <f t="shared" si="1"/>
-        <v>18.092372851443461</v>
-      </c>
-      <c r="O45">
-        <f t="shared" si="2"/>
-        <v>7.3786401162349788</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+        <v>11.160717469115211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -15755,20 +15406,12 @@
       <c r="L46" s="2">
         <v>0</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="2">
         <f t="shared" si="0"/>
-        <v>67.291710997688995</v>
-      </c>
-      <c r="N46">
-        <f t="shared" si="1"/>
-        <v>16.29949937742045</v>
-      </c>
-      <c r="O46">
-        <f t="shared" si="2"/>
-        <v>8.6622815135051265</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+        <v>13.102316292327984</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
@@ -15805,20 +15448,12 @@
       <c r="L47" s="2">
         <v>0</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="2">
         <f t="shared" si="0"/>
-        <v>65.357708998847698</v>
-      </c>
-      <c r="N47">
-        <f t="shared" si="1"/>
-        <v>10.503694668845675</v>
-      </c>
-      <c r="O47">
-        <f t="shared" si="2"/>
-        <v>12.742884853257225</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+        <v>19.274518793205552</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>59</v>
       </c>
@@ -15855,17 +15490,9 @@
       <c r="L48" s="2">
         <v>0</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="2">
         <f t="shared" si="0"/>
-        <v>62.551981308056448</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="1"/>
-        <v>12.211347057323232</v>
-      </c>
-      <c r="O48">
-        <f t="shared" si="2"/>
-        <v>13.322564257351718</v>
+        <v>20.151325081335635</v>
       </c>
     </row>
   </sheetData>
